--- a/tran.xlsx
+++ b/tran.xlsx
@@ -1259,7 +1259,7 @@
         <v>5.95</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>-120</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="3">
@@ -1273,7 +1273,7 @@
         <v>6.95</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>-120</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>7.95</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-120</v>
+        <v>7.95</v>
       </c>
     </row>
   </sheetData>
